--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,12 +662,101 @@
           <t>NSE:HINDZINC26SEP600CE</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:17:42</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1252.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1260</v>
+      </c>
+      <c r="I3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="K3" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="L3" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="M3" t="n">
+        <v>46.44</v>
+      </c>
+      <c r="N3" t="n">
+        <v>625</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="S3" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="U3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>NSE:LODHA26SEP1260CE</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -662,6 +662,11 @@
           <t>NSE:HINDZINC26SEP600CE</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:24:01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -751,12 +756,6 @@
           <t>NSE:LODHA26SEP1260CE</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -754,6 +754,100 @@
       <c r="W3" t="inlineStr">
         <is>
           <t>NSE:LODHA26SEP1260CE</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:25:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:25:35</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1152.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1160</v>
+      </c>
+      <c r="I4" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="K4" t="n">
+        <v>33.43</v>
+      </c>
+      <c r="L4" t="n">
+        <v>37.17</v>
+      </c>
+      <c r="M4" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="N4" t="n">
+        <v>625</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="S4" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>64.91</v>
+      </c>
+      <c r="U4" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Metals</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>NSE:JINDALSTEL26SEP1160CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -850,6 +850,11 @@
           <t>NSE:JINDALSTEL26SEP1160CE</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:27:10</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -756,11 +756,7 @@
           <t>NSE:LODHA26SEP1260CE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-31 09:25:35</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -756,7 +756,11 @@
           <t>NSE:LODHA26SEP1260CE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:35:01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -855,6 +855,101 @@
           <t>2026-08-31 09:27:10</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:28:53</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>288</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="H5" t="n">
+        <v>290</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="L5" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="M5" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="S5" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="T5" t="n">
+        <v>46.43</v>
+      </c>
+      <c r="U5" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>NSE:ANGELONE26SEP290PE</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -944,12 +944,11 @@
           <t>NSE:ANGELONE26SEP290PE</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:50:28</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -944,11 +944,7 @@
           <t>NSE:ANGELONE26SEP290PE</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-08-31 10:50:28</t>
-        </is>
-      </c>
+      <c r="AC5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -944,7 +944,101 @@
           <t>NSE:ANGELONE26SEP290PE</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:34:19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>4498.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I6" t="n">
+        <v>128.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>101.59</v>
+      </c>
+      <c r="K6" t="n">
+        <v>153.28</v>
+      </c>
+      <c r="L6" t="n">
+        <v>167.91</v>
+      </c>
+      <c r="M6" t="n">
+        <v>187.41</v>
+      </c>
+      <c r="N6" t="n">
+        <v>150</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="S6" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="U6" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Alcohol</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NSE:RADICO26SEP4500CE</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -1033,12 +1033,11 @@
           <t>NSE:RADICO26SEP4500CE</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:43:55</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -1033,11 +1033,7 @@
           <t>NSE:RADICO26SEP4500CE</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-08-31 11:43:55</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -1033,7 +1033,11 @@
           <t>NSE:RADICO26SEP4500CE</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:51:46</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -944,6 +944,11 @@
           <t>NSE:ANGELONE26SEP290PE</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:36:40</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -944,9 +944,14 @@
           <t>NSE:ANGELONE26SEP290PE</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-31 13:36:40</t>
+          <t>2026-08-31 13:37:56</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -949,11 +949,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:37:56</t>
-        </is>
-      </c>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -944,12 +944,16 @@
           <t>NSE:ANGELONE26SEP290PE</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:51:19</t>
+        </is>
+      </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -954,6 +954,11 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:51:58</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -949,9 +949,14 @@
           <t>2026-08-31 13:51:19</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:52:19</t>
+        </is>
+      </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -954,9 +954,14 @@
           <t>2026-08-31 13:52:19</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:55:09</t>
+        </is>
+      </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Target 2 Hit</t>
+          <t>Target 3 Hit</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -964,11 +964,7 @@
           <t>Target 3 Hit</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-08-31 13:51:58</t>
-        </is>
-      </c>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -964,7 +964,11 @@
           <t>Target 3 Hit</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:01:42</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,6 +1063,101 @@
           <t>2026-08-31 11:51:46</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:46:53</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>708.35</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="H7" t="n">
+        <v>710</v>
+      </c>
+      <c r="I7" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="K7" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="L7" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="M7" t="n">
+        <v>19.53</v>
+      </c>
+      <c r="N7" t="n">
+        <v>650</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="S7" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>34.18</v>
+      </c>
+      <c r="U7" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>NSE:HDFCBANK26SEP710PE</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -1152,12 +1152,16 @@
           <t>NSE:HDFCBANK26SEP710PE</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:48:30</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1162,6 +1162,101 @@
           <t>2026-08-31 14:48:30</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:55:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1565.1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1560</v>
+      </c>
+      <c r="I8" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="J8" t="n">
+        <v>38.05</v>
+      </c>
+      <c r="K8" t="n">
+        <v>61.71</v>
+      </c>
+      <c r="L8" t="n">
+        <v>68.41</v>
+      </c>
+      <c r="M8" t="n">
+        <v>77.34</v>
+      </c>
+      <c r="N8" t="n">
+        <v>425</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="S8" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>70.33</v>
+      </c>
+      <c r="U8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Plastics</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NSE:ASTRAL26SEP1560CE</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -1251,12 +1251,16 @@
           <t>NSE:ASTRAL26SEP1560CE</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:56:52</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -1256,11 +1256,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-31 14:56:52</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1256,7 +1256,100 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:03:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:03:26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>95.02</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-3.35</v>
+      </c>
+      <c r="H9" t="n">
+        <v>95</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6975</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="S9" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="U9" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NSE:GMRAIRPORT26SEP95PE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -1256,11 +1256,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-31 15:03:26</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -1256,7 +1256,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:08:26</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -1256,11 +1256,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-31 15:08:26</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1256,7 +1256,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1346,6 +1345,101 @@
           <t>NSE:GMRAIRPORT26SEP95PE</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:11:45</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>203.02</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-4.52</v>
+      </c>
+      <c r="H10" t="n">
+        <v>205</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3550</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="S10" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="U10" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NSE:ADANIPOWER26SEP205PE</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -1345,6 +1345,16 @@
           <t>NSE:GMRAIRPORT26SEP95PE</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:16:40</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1434,12 +1444,6 @@
           <t>NSE:ADANIPOWER26SEP205PE</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -1350,11 +1350,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-31 15:16:40</t>
-        </is>
-      </c>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -1251,9 +1251,14 @@
           <t>NSE:ASTRAL26SEP1560CE</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:30:34</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>SL Hit</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1355,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1261,6 +1261,11 @@
           <t>SL Hit</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:31:38</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1442,6 +1447,283 @@
       <c r="W10" t="inlineStr">
         <is>
           <t>NSE:ADANIPOWER26SEP205PE</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:31:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:31:38</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="H11" t="n">
+        <v>255</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1725</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="S11" t="n">
+        <v>22</v>
+      </c>
+      <c r="T11" t="n">
+        <v>21.62</v>
+      </c>
+      <c r="U11" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>NSE:ITC26SEP255PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:31:38</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1897.6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1900</v>
+      </c>
+      <c r="I12" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="J12" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="K12" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="L12" t="n">
+        <v>78.93000000000001</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.37</v>
+      </c>
+      <c r="N12" t="n">
+        <v>275</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="S12" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>32.34</v>
+      </c>
+      <c r="U12" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>NSE:COLPAL26SEP1900PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:31:38</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>356.7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="H13" t="n">
+        <v>355</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="L13" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="S13" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>52</v>
+      </c>
+      <c r="U13" t="n">
+        <v>33</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>NSE:FEDERALBNK26SEP355CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -850,6 +850,16 @@
           <t>NSE:JINDALSTEL26SEP1160CE</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:33:04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>2026-08-31 09:27:10</t>

--- a/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
+++ b/backend/signal_logs/2026-08-31/signals_2026-08-31.xlsx
@@ -662,6 +662,11 @@
           <t>NSE:HINDZINC26SEP600CE</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Closed down ~19.2 (-7.0% from entry)</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>2026-08-31 09:24:01</t>
@@ -756,6 +761,11 @@
           <t>NSE:LODHA26SEP1260CE</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Closed down ~22.0 (-16.7% from entry)</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>2026-08-31 09:35:01</t>
@@ -1068,6 +1078,11 @@
           <t>NSE:RADICO26SEP4500CE</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Closed down ~125.0 (-3.0% from entry)</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>2026-08-31 11:51:46</t>
@@ -1558,6 +1573,11 @@
           <t>NSE:ITC26SEP255PE</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Closed flat ~1.5 (+0.0% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1647,6 +1667,11 @@
           <t>NSE:COLPAL26SEP1900PE</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Closed down ~62.35 (-5.6% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1734,6 +1759,11 @@
       <c r="W13" t="inlineStr">
         <is>
           <t>NSE:FEDERALBNK26SEP355CE</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Closed up ~5.2 (+2.0% from entry, EOD estimate)</t>
         </is>
       </c>
     </row>
